--- a/military_final.xlsx
+++ b/military_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\Unified-Military-Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1B101C-7546-4B0D-9051-6568FF0F8808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7210915-1E1B-4459-A3C2-A58A1299611F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1119,6 +1119,7 @@
   <dimension ref="A1:BW146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="70" max="70" width="17" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
